--- a/ANm/Lanyuak_Barley_results.xlsx
+++ b/ANm/Lanyuak_Barley_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>100.2943774154442</v>
+        <v>105.0674828219032</v>
       </c>
       <c r="C3" t="n">
         <v>113.9409026286368</v>
       </c>
       <c r="D3" t="n">
-        <v>13.64652521319267</v>
+        <v>8.873419806733622</v>
       </c>
       <c r="E3" t="n">
-        <v>13.64797914079006</v>
+        <v>8.874873734331004</v>
       </c>
       <c r="F3" t="n">
-        <v>50.04259018289687</v>
+        <v>32.54120369254701</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>92.55674038070875</v>
+        <v>100.0426037738516</v>
       </c>
       <c r="C4" t="n">
         <v>113.9409017419045</v>
       </c>
       <c r="D4" t="n">
-        <v>21.38416136119571</v>
+        <v>13.89829796805282</v>
       </c>
       <c r="E4" t="n">
-        <v>7.737636148003034</v>
+        <v>5.024878161319194</v>
       </c>
       <c r="F4" t="n">
-        <v>28.37133254267779</v>
+        <v>18.42455325817038</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>87.26706245123209</v>
+        <v>96.61770248194898</v>
       </c>
       <c r="C5" t="n">
         <v>113.9409009003157</v>
       </c>
       <c r="D5" t="n">
-        <v>26.67383844908359</v>
+        <v>17.3231984183667</v>
       </c>
       <c r="E5" t="n">
-        <v>5.289677087887881</v>
+        <v>3.424900450313885</v>
       </c>
       <c r="F5" t="n">
-        <v>19.3954826555889</v>
+        <v>12.55796831781758</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>83.3001304534062</v>
+        <v>94.06140954505675</v>
       </c>
       <c r="C6" t="n">
         <v>113.9409001015723</v>
       </c>
       <c r="D6" t="n">
-        <v>30.64076964816611</v>
+        <v>19.87949055651556</v>
       </c>
       <c r="E6" t="n">
-        <v>3.966931199082524</v>
+        <v>2.556292138148862</v>
       </c>
       <c r="F6" t="n">
-        <v>14.54541439663592</v>
+        <v>9.373071173212495</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>80.07254184449158</v>
+        <v>91.99405802181964</v>
       </c>
       <c r="C7" t="n">
         <v>113.940899343493</v>
       </c>
       <c r="D7" t="n">
-        <v>33.86835749900141</v>
+        <v>21.94684132167335</v>
       </c>
       <c r="E7" t="n">
-        <v>3.227587850835292</v>
+        <v>2.067350765157784</v>
       </c>
       <c r="F7" t="n">
-        <v>11.83448878639607</v>
+        <v>7.580286138911873</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>77.2780541723031</v>
+        <v>90.21596111739927</v>
       </c>
       <c r="C8" t="n">
         <v>113.9408986240075</v>
       </c>
       <c r="D8" t="n">
-        <v>36.66284445170442</v>
+        <v>23.72493750660824</v>
       </c>
       <c r="E8" t="n">
-        <v>2.794486952703011</v>
+        <v>1.778096184934896</v>
       </c>
       <c r="F8" t="n">
-        <v>10.24645215991104</v>
+        <v>6.51968601142795</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>74.75422433821322</v>
+        <v>88.62087017808017</v>
       </c>
       <c r="C9" t="n">
         <v>113.9408979411511</v>
       </c>
       <c r="D9" t="n">
-        <v>39.18667360293792</v>
+        <v>25.32002776307097</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5238291512335</v>
+        <v>1.595090256462726</v>
       </c>
       <c r="F9" t="n">
-        <v>9.254040221189499</v>
+        <v>5.84866427369666</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>72.4138493230862</v>
+        <v>87.1514681680213</v>
       </c>
       <c r="C10" t="n">
         <v>113.940897293059</v>
       </c>
       <c r="D10" t="n">
-        <v>41.5270479699728</v>
+        <v>26.7894291250377</v>
       </c>
       <c r="E10" t="n">
-        <v>2.340374367034883</v>
+        <v>1.469401361966732</v>
       </c>
       <c r="F10" t="n">
-        <v>8.581372679127904</v>
+        <v>5.387804993878016</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>70.2093062616578</v>
+        <v>85.77620839231534</v>
       </c>
       <c r="C11" t="n">
         <v>113.9408966779613</v>
       </c>
       <c r="D11" t="n">
-        <v>43.73159041630346</v>
+        <v>28.16468828564592</v>
       </c>
       <c r="E11" t="n">
-        <v>2.204542446330663</v>
+        <v>1.375259160608223</v>
       </c>
       <c r="F11" t="n">
-        <v>8.083322303212432</v>
+        <v>5.042616922230152</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>68.11387953882989</v>
+        <v>84.47717890784948</v>
       </c>
       <c r="C12" t="n">
         <v>113.9408960941782</v>
       </c>
       <c r="D12" t="n">
-        <v>45.82701655534832</v>
+        <v>29.46371718632874</v>
       </c>
       <c r="E12" t="n">
-        <v>2.095426139044861</v>
+        <v>1.299028900682814</v>
       </c>
       <c r="F12" t="n">
-        <v>7.683229176497822</v>
+        <v>4.763105969170316</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>66.11194473568013</v>
+        <v>83.24371858531251</v>
       </c>
       <c r="C13" t="n">
         <v>113.9408955401156</v>
       </c>
       <c r="D13" t="n">
-        <v>47.82895080443545</v>
+        <v>30.69717695480307</v>
       </c>
       <c r="E13" t="n">
-        <v>2.001934249087128</v>
+        <v>1.233459768474333</v>
       </c>
       <c r="F13" t="n">
-        <v>7.340425579986136</v>
+        <v>4.52268581773922</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>64.19379605970192</v>
+        <v>82.06905040178566</v>
       </c>
       <c r="C14" t="n">
         <v>113.9408950142603</v>
       </c>
       <c r="D14" t="n">
-        <v>49.7470989545584</v>
+        <v>31.87184461247466</v>
       </c>
       <c r="E14" t="n">
-        <v>1.918148150122946</v>
+        <v>1.174667657671591</v>
       </c>
       <c r="F14" t="n">
-        <v>7.033209883784134</v>
+        <v>4.307114744795835</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>62.35291591202911</v>
+        <v>80.94850254904078</v>
       </c>
       <c r="C15" t="n">
         <v>113.9408945151764</v>
       </c>
       <c r="D15" t="n">
-        <v>51.58797860314726</v>
+        <v>32.99239196613559</v>
       </c>
       <c r="E15" t="n">
-        <v>1.84087964858886</v>
+        <v>1.120547353660925</v>
       </c>
       <c r="F15" t="n">
-        <v>6.74989204482582</v>
+        <v>4.108673630090057</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>60.58453116829559</v>
+        <v>79.87856666138417</v>
       </c>
       <c r="C16" t="n">
         <v>113.9408940415008</v>
       </c>
       <c r="D16" t="n">
-        <v>53.35636287320521</v>
+        <v>34.06232738011663</v>
       </c>
       <c r="E16" t="n">
-        <v>1.76838427005795</v>
+        <v>1.069935413981042</v>
       </c>
       <c r="F16" t="n">
-        <v>6.484075656879152</v>
+        <v>3.923096517930489</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>58.88484815619763</v>
+        <v>78.85639788730445</v>
       </c>
       <c r="C17" t="n">
         <v>113.9408935919401</v>
       </c>
       <c r="D17" t="n">
-        <v>55.0560454357425</v>
+        <v>35.08449570463567</v>
       </c>
       <c r="E17" t="n">
-        <v>1.699682562537291</v>
+        <v>1.022168324519043</v>
       </c>
       <c r="F17" t="n">
-        <v>6.232169395970065</v>
+        <v>3.747950523236492</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>57.250645904065</v>
+        <v>77.87954836762272</v>
       </c>
       <c r="C18" t="n">
         <v>113.9408931652666</v>
       </c>
       <c r="D18" t="n">
-        <v>56.6902472612016</v>
+        <v>36.06134479764388</v>
       </c>
       <c r="E18" t="n">
-        <v>1.634201825459101</v>
+        <v>0.9768490930082123</v>
       </c>
       <c r="F18" t="n">
-        <v>5.992073360016704</v>
+        <v>3.581780007696779</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>55.67905865092689</v>
+        <v>76.94582411253154</v>
       </c>
       <c r="C19" t="n">
         <v>113.940892760315</v>
       </c>
       <c r="D19" t="n">
-        <v>58.26183410938813</v>
+        <v>36.99506864778348</v>
       </c>
       <c r="E19" t="n">
-        <v>1.571586848186534</v>
+        <v>0.9337238501396001</v>
       </c>
       <c r="F19" t="n">
-        <v>5.762485110017292</v>
+        <v>3.423654117178534</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>54.16745842571743</v>
+        <v>76.05320718733299</v>
       </c>
       <c r="C20" t="n">
         <v>113.9408923759796</v>
       </c>
       <c r="D20" t="n">
-        <v>59.77343395026215</v>
+        <v>37.8876851886466</v>
       </c>
       <c r="E20" t="n">
-        <v>1.51159984087402</v>
+        <v>0.8926165408631164</v>
       </c>
       <c r="F20" t="n">
-        <v>5.542532749871405</v>
+        <v>3.272927316498093</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>52.71339060745157</v>
+        <v>75.19981251993448</v>
       </c>
       <c r="C21" t="n">
         <v>113.9408920112107</v>
       </c>
       <c r="D21" t="n">
-        <v>61.22750140375911</v>
+        <v>38.7410794912762</v>
       </c>
       <c r="E21" t="n">
-        <v>1.454067453496954</v>
+        <v>0.8533943026295958</v>
       </c>
       <c r="F21" t="n">
-        <v>5.331580662822165</v>
+        <v>3.129112442975185</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>51.31453759790476</v>
+        <v>74.38386311324398</v>
       </c>
       <c r="C22" t="n">
         <v>113.9408916650122</v>
       </c>
       <c r="D22" t="n">
-        <v>62.62635406710744</v>
+        <v>39.55702855176823</v>
       </c>
       <c r="E22" t="n">
-        <v>1.398852663348336</v>
+        <v>0.8159490604920308</v>
       </c>
       <c r="F22" t="n">
-        <v>5.129126432277232</v>
+        <v>2.991813221804113</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>49.96869746761914</v>
+        <v>73.60367508846997</v>
       </c>
       <c r="C23" t="n">
         <v>113.9408913364387</v>
       </c>
       <c r="D23" t="n">
-        <v>63.97219386881956</v>
+        <v>40.33721624796873</v>
       </c>
       <c r="E23" t="n">
-        <v>1.345839801712117</v>
+        <v>0.7801876962004997</v>
       </c>
       <c r="F23" t="n">
-        <v>4.934745939611095</v>
+        <v>2.860688219401832</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>48.67377062898676</v>
+        <v>72.85764802298785</v>
       </c>
       <c r="C24" t="n">
         <v>113.9408910245929</v>
       </c>
       <c r="D24" t="n">
-        <v>65.26712039560613</v>
+        <v>41.08324300160504</v>
       </c>
       <c r="E24" t="n">
-        <v>1.294926526786568</v>
+        <v>0.7460267536363148</v>
       </c>
       <c r="F24" t="n">
-        <v>4.74806393155075</v>
+        <v>2.735431429999821</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>47.42775086059033</v>
+        <v>72.14425817990262</v>
       </c>
       <c r="C25" t="n">
         <v>113.9408907286231</v>
       </c>
       <c r="D25" t="n">
-        <v>66.51313986803282</v>
+        <v>41.79663254872052</v>
       </c>
       <c r="E25" t="n">
-        <v>1.246019472426696</v>
+        <v>0.713389547115483</v>
       </c>
       <c r="F25" t="n">
-        <v>4.56873806556455</v>
+        <v>2.615761672756771</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>46.22871873445462</v>
+        <v>71.46205335401086</v>
       </c>
       <c r="C26" t="n">
         <v>113.9408904477213</v>
       </c>
       <c r="D26" t="n">
-        <v>67.7121717132667</v>
+        <v>42.47883709371045</v>
       </c>
       <c r="E26" t="n">
-        <v>1.199031845233876</v>
+        <v>0.6822045449899292</v>
       </c>
       <c r="F26" t="n">
-        <v>4.396450099190877</v>
+        <v>2.501416664963074</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>45.07483641061747</v>
+        <v>70.80964865500637</v>
       </c>
       <c r="C27" t="n">
         <v>113.9408901811202</v>
       </c>
       <c r="D27" t="n">
-        <v>68.8660537705027</v>
+        <v>43.1312415261138</v>
       </c>
       <c r="E27" t="n">
-        <v>1.153882057236004</v>
+        <v>0.652404432403344</v>
       </c>
       <c r="F27" t="n">
-        <v>4.230900876532014</v>
+        <v>2.392149585478928</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>43.96434324593594</v>
+        <v>70.18572286412315</v>
       </c>
       <c r="C28" t="n">
         <v>113.9408899280917</v>
       </c>
       <c r="D28" t="n">
-        <v>69.9765466821558</v>
+        <v>43.75516706396859</v>
       </c>
       <c r="E28" t="n">
-        <v>1.110492911653097</v>
+        <v>0.6239255378547881</v>
       </c>
       <c r="F28" t="n">
-        <v>4.071807342728022</v>
+        <v>2.287726972134223</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>42.895551919313</v>
+        <v>69.58901516737124</v>
       </c>
       <c r="C29" t="n">
         <v>113.9408896879449</v>
       </c>
       <c r="D29" t="n">
-        <v>71.04533776863195</v>
+        <v>44.3518745205737</v>
       </c>
       <c r="E29" t="n">
-        <v>1.068791086476153</v>
+        <v>0.5967074566051167</v>
       </c>
       <c r="F29" t="n">
-        <v>3.918900650412562</v>
+        <v>2.187927340885428</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>41.8668449107566</v>
+        <v>69.01832215705548</v>
       </c>
       <c r="C30" t="n">
         <v>113.9408894600241</v>
       </c>
       <c r="D30" t="n">
-        <v>72.0740445492675</v>
+        <v>44.92256730296862</v>
       </c>
       <c r="E30" t="n">
-        <v>1.028706780635545</v>
+        <v>0.5706927823949144</v>
       </c>
       <c r="F30" t="n">
-        <v>3.771924862330332</v>
+        <v>2.092540202114686</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>40.87667124347823</v>
+        <v>68.47249504033819</v>
       </c>
       <c r="C31" t="n">
         <v>113.9408892437067</v>
       </c>
       <c r="D31" t="n">
-        <v>73.06421800022844</v>
+        <v>45.46839420336848</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9901734509609383</v>
+        <v>0.5458269003998595</v>
       </c>
       <c r="F31" t="n">
-        <v>3.630635986856774</v>
+        <v>2.001365301466151</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>39.9235434365049</v>
+        <v>67.95043701874455</v>
       </c>
       <c r="C32" t="n">
         <v>113.9408890384019</v>
       </c>
       <c r="D32" t="n">
-        <v>74.01734560189702</v>
+        <v>45.99045201965737</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9531276016685837</v>
+        <v>0.5220578162888927</v>
       </c>
       <c r="F32" t="n">
-        <v>3.49480120611814</v>
+        <v>1.914211993059273</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>39.00603463580617</v>
+        <v>67.45110081603939</v>
       </c>
       <c r="C33" t="n">
         <v>113.9408888435493</v>
       </c>
       <c r="D33" t="n">
-        <v>74.93485420774311</v>
+        <v>46.4897880275099</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9175086058460948</v>
+        <v>0.4993360078525342</v>
       </c>
       <c r="F33" t="n">
-        <v>3.364198221435681</v>
+        <v>1.830898695459292</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>38.12277590307331</v>
+        <v>66.97348633927884</v>
       </c>
       <c r="C34" t="n">
         <v>113.9408886586166</v>
       </c>
       <c r="D34" t="n">
-        <v>75.81811275554332</v>
+        <v>46.96740231933781</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8832585478002102</v>
+        <v>0.4776142918279049</v>
       </c>
       <c r="F34" t="n">
-        <v>3.238614675267437</v>
+        <v>1.751252403368985</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>37.27245364743807</v>
+        <v>66.51663846194927</v>
       </c>
       <c r="C35" t="n">
         <v>113.9408884830989</v>
       </c>
       <c r="D35" t="n">
-        <v>76.66843483566086</v>
+        <v>47.42425002114966</v>
       </c>
       <c r="E35" t="n">
-        <v>0.850322080117536</v>
+        <v>0.4568477018118529</v>
       </c>
       <c r="F35" t="n">
-        <v>3.117847627097632</v>
+        <v>1.675108239976794</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>36.4538071889159</v>
+        <v>66.07964492047017</v>
       </c>
       <c r="C36" t="n">
         <v>113.9408883165168</v>
       </c>
       <c r="D36" t="n">
-        <v>77.48708112760093</v>
+        <v>47.86124339604666</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8186462919400697</v>
+        <v>0.4369933748969999</v>
       </c>
       <c r="F36" t="n">
-        <v>3.001703070446922</v>
+        <v>1.602309041289</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>35.66562644443538</v>
+        <v>65.6616343167679</v>
       </c>
       <c r="C37" t="n">
         <v>113.9408881584154</v>
       </c>
       <c r="D37" t="n">
-        <v>78.27526171398</v>
+        <v>48.27925384164747</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7881805863790703</v>
+        <v>0.4180104456008138</v>
       </c>
       <c r="F37" t="n">
-        <v>2.889995483389924</v>
+        <v>1.532704967202984</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>34.90674972862406</v>
+        <v>65.26177422054987</v>
       </c>
       <c r="C38" t="n">
         <v>113.9408880083629</v>
       </c>
       <c r="D38" t="n">
-        <v>79.03413827973884</v>
+        <v>48.67911378781304</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7588765657588397</v>
+        <v>0.399859946165563</v>
       </c>
       <c r="F38" t="n">
-        <v>2.782547407782412</v>
+        <v>1.466153135940398</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>34.17606166240934</v>
+        <v>64.87926936555212</v>
       </c>
       <c r="C39" t="n">
         <v>113.9408878659496</v>
       </c>
       <c r="D39" t="n">
-        <v>79.7648262035403</v>
+        <v>49.06161850039751</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7306879238014545</v>
+        <v>0.3825047125844776</v>
       </c>
       <c r="F39" t="n">
-        <v>2.679189053938666</v>
+        <v>1.402517279476418</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>33.47249118314318</v>
+        <v>64.51335993451708</v>
       </c>
       <c r="C40" t="n">
         <v>113.9408877307867</v>
       </c>
       <c r="D40" t="n">
-        <v>80.46839654764347</v>
+        <v>49.42752779626957</v>
       </c>
       <c r="E40" t="n">
-        <v>0.70357034410317</v>
+        <v>0.3659092958720578</v>
       </c>
       <c r="F40" t="n">
-        <v>2.57975792837829</v>
+        <v>1.341667418197545</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>32.79500965047141</v>
+        <v>64.16331992804905</v>
       </c>
       <c r="C41" t="n">
         <v>113.9408876025048</v>
       </c>
       <c r="D41" t="n">
-        <v>81.1458779520334</v>
+        <v>49.77756767445577</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6774814043899369</v>
+        <v>0.3500398781861946</v>
       </c>
       <c r="F41" t="n">
-        <v>2.484098482763102</v>
+        <v>1.28347955334938</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>32.14262904259536</v>
+        <v>63.82845561282465</v>
       </c>
       <c r="C42" t="n">
         <v>113.9408874807538</v>
       </c>
       <c r="D42" t="n">
-        <v>81.79825843815843</v>
+        <v>50.11243186792914</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6523804861250255</v>
+        <v>0.334864193473372</v>
       </c>
       <c r="F42" t="n">
-        <v>2.392061782458427</v>
+        <v>1.227835376069031</v>
       </c>
     </row>
   </sheetData>
